--- a/rabbit-web-app/public/sample_excels/dispatch/carrier_single_sample.xlsx
+++ b/rabbit-web-app/public/sample_excels/dispatch/carrier_single_sample.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Carrier" sheetId="1" r:id="rId1"/>
+    <sheet name="Carriers" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,17 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
-  <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="45.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:F2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -417,22 +407,16 @@
         <v>address</v>
       </c>
       <c r="C1" t="str">
-        <v>mcNumber</v>
+        <v>primaryContact</v>
       </c>
       <c r="D1" t="str">
-        <v>dotNumber</v>
+        <v>email</v>
       </c>
       <c r="E1" t="str">
-        <v>primaryContact</v>
+        <v>cellPhone</v>
       </c>
       <c r="F1" t="str">
-        <v>email</v>
-      </c>
-      <c r="G1" t="str">
-        <v>phone</v>
-      </c>
-      <c r="H1" t="str">
-        <v>cellPhone</v>
+        <v>telephone</v>
       </c>
     </row>
     <row r="2">
@@ -443,27 +427,21 @@
         <v>Giriraj Annexe, Circuit House Road, Hubballi, Karnataka</v>
       </c>
       <c r="C2" t="str">
-        <v>MC-847291</v>
+        <v>Anand Sankeshwar</v>
       </c>
       <c r="D2" t="str">
-        <v>DOT-3920194</v>
+        <v>dispatch@vrllogistics.in</v>
       </c>
       <c r="E2" t="str">
-        <v>Anand Sankeshwar</v>
+        <v>94481 23456</v>
       </c>
       <c r="F2" t="str">
-        <v>dispatch@vrllogistics.in</v>
-      </c>
-      <c r="G2" t="str">
-        <v>+91 836 2237511</v>
-      </c>
-      <c r="H2" t="str">
-        <v>+91 94481 23456</v>
+        <v>836 2237511</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rabbit-web-app/public/sample_excels/dispatch/carrier_single_sample.xlsx
+++ b/rabbit-web-app/public/sample_excels/dispatch/carrier_single_sample.xlsx
@@ -397,26 +397,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
+  <cols>
+    <col min="1" max="1" width="21.83203125" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="28.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>name</v>
+        <v>Carrier Name</v>
       </c>
       <c r="B1" t="str">
-        <v>address</v>
+        <v>MC Number</v>
       </c>
       <c r="C1" t="str">
-        <v>primaryContact</v>
+        <v>DOT Number</v>
       </c>
       <c r="D1" t="str">
-        <v>email</v>
+        <v>Address</v>
       </c>
       <c r="E1" t="str">
-        <v>cellPhone</v>
+        <v>Primary Contact</v>
       </c>
       <c r="F1" t="str">
-        <v>telephone</v>
+        <v>Email</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Cell Phone</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Telephone</v>
       </c>
     </row>
     <row r="2">
@@ -424,24 +440,30 @@
         <v>VRL Logistics Ltd</v>
       </c>
       <c r="B2" t="str">
+        <v>874512</v>
+      </c>
+      <c r="C2" t="str">
+        <v>3498120</v>
+      </c>
+      <c r="D2" t="str">
         <v>Giriraj Annexe, Circuit House Road, Hubballi, Karnataka</v>
       </c>
-      <c r="C2" t="str">
+      <c r="E2" t="str">
         <v>Anand Sankeshwar</v>
       </c>
-      <c r="D2" t="str">
+      <c r="F2" t="str">
         <v>dispatch@vrllogistics.in</v>
       </c>
-      <c r="E2" t="str">
+      <c r="G2" t="str">
         <v>94481 23456</v>
       </c>
-      <c r="F2" t="str">
+      <c r="H2" t="str">
         <v>836 2237511</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
   </ignoredErrors>
 </worksheet>
 </file>